--- a/extenbooks/S502.xlsx
+++ b/extenbooks/S502.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=billions_usd</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BEA GDPbyIndustry, units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S502-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S502-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S502-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>198.47</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>198.47</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>189.06</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>189.06</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>212.56</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>212.56</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>244.59</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>244.59</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>254.35</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>254.35</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>268.66</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>268.66</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>261.3</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>261.3</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>287.18</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>287.18</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>303.11</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>303.11</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>314.63</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>314.63</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>308</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>308</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>334.93</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>334.93</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>343.72</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>343.72</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>347.54</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>347.54</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>371.4</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>389.68</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>389.68</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>412.31</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>412.31</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>447.41</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>447.41</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>483.74</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>483.74</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>500.66</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>500.66</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>545.14</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>545.14</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>586.54</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>586.54</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>602.47</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>602.47</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>644.7</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>644.7</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>714.33</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>714.33</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>837.4</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>837.4</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>926.5599999999999</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>926.5599999999999</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>1023.78</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>1023.78</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>1187.33</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>1187.33</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>1367.27</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>1367.27</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>1545.89</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>1545.89</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>1710.49</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>1710.49</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>1851.27</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>1851.27</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>2078.34</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>2078.34</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>2114.61</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>2114.61</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>2235.61</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>2235.61</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>2497.25</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>2497.25</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>2618.65</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>2618.65</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>2664.48</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>2664.48</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>2808.66</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>2808.66</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>3122.99</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>3122.99</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,502 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>3278.25</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3278.25</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>3355.011886423566</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3433.571191350084</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>3513.970002245421</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3596.251392074812</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>3680.459442378795</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>3766.639266889561</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>3854.837035700212</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>3945.1</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>3945.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>3977.3</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>3977.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>4186.700000000001</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>4186.700000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>4504.799999999999</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>4504.799999999999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>4379.200000000001</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>4379.200000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>4238.599999999999</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>4238.599999999999</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>4402</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>4402</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>4833.9</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>4833.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>5436.000000000001</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>5436.000000000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>5729.1</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>5729.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>6098.499999999999</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>6098.499999999999</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6399.099999999999</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>6399.099999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>4944</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>5684.499999999999</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>5684.499999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>6471.3</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>6471.3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>6751.1</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>6751.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>7029.6</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>7029.6</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>7345.5</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>7345.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>6866.6</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>6866.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>6719.7</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>6719.7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>7069.900000000001</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>7069.900000000001</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>7618</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>7618</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>7511</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>7511</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>6838.9</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>6838.9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>8409.899999999998</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>8409.899999999998</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>9804.499999999998</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>9804.499999999998</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>9348.499999999998</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>9348.499999999998</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>9367.299999999999</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>9367.299999999999</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1688,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1929–2025</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -936,7 +1700,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -948,7 +1712,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_4</t>
+          <t>Fig_5_4, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,166 +1754,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S502-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S502-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BEA GDPbyIndustry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S502-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S502 — Constant Capital (C*_m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix H.1 (cross-checked vs. Appendix E.2 column `C_star_m` for 1948-1961 overlap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via n/a (book period only) when API access provisioned)</t>
+          <t># S502 — Constant Capital (C*_m)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix H.1 (cross-checked vs. Appendix E.2 column `C_star_m` for 1948-1961 overlap)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1989 (book period; extension via n/a (book period only) when API access provisioned)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: validated_book_and_extension</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Constant capital consumed in production (M'_p in book notation, C*_m in extended notation). Subtracted from TP* to yield GFP.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Constant capital consumed in production (M'_p in book notation, C*_m in extended notation). Subtracted from TP* to yield GFP.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>| `S502-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>| `S502-COMBINED` |  | 1948-1989 | billions_dollars |</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
@@ -1161,207 +1934,203 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| Subseries | Source | Period | Units |</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>|---|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>| `S502-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>| `S502-COMBINED` |  | 1948-1989 | billions_dollars |</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>### S502-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2. Extract column `Mp` (and the `year` index).</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>### S502-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Reference cross-check: Appendix E.2 column `C_star_m` provides the same values for 1948-1961 — V03 validates the H.1-derived series against E.2 row-by-row.</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>2. Extract column `Mp` (and the `year` index).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3. No further transformation — this is the canonical published value.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Reference cross-check: Appendix E.2 column `C_star_m` provides the same values for 1948-1961 — V03 validates the H.1-derived series against E.2 row-by-row.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1948=198.47</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S502_constant_capital.py` writes to `data/intermediate/validation/S502.json`.</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1948=198.47</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S502_constant_capital.py` writes to `data/intermediate/validation/S502.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S502_constant_capital.py</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S502.csv</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S502_constant_capital.py</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S502.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1369,7 +2138,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S502_constant_capital.py</t>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
         </is>
       </c>
     </row>
@@ -1377,65 +2146,105 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S502_constant_capital.py</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S502.csv</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S502_constant_capital.py</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S502.csv</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S502_constant_capital.py</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1452,10 +2261,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1480,180 +2289,313 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C*_m represents the intermediate inputs consumed by productive sectors (materials-flow constant capital). It is the sum of all intermediate purchases by productive and trading industries. C*_m = total intermediate inputs of productive + trading sectors from IO tables.</t>
+          <t>C*m = M'p = materials inputs into production; C*d = {Dp} = depreciation of productive fixed capital; C* = M'p + Dp = constant capital used up (flow).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/tables/page_340_variables_definitions.csv</t>
+          <t>ST_1994, Ch5, p.95; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Subseries A only (1948-1989): digitized from book Table E.2. No extension subseries exists because detailed IO intermediate input data at the required sectoral granularity is not straightforwardly available from BEA for modern periods without full IO table reconstruction.</t>
+          <t>Materials used up C*m and productive use U*m: Both net of depreciation. C*m = C* - Depreciation. Simply equal to M'p (sum of first two entries in top left corner of the IO table).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/tables/page_310_table_E2.csv</t>
+          <t>ST_1994, Ch5, p.92; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.4 shows C*_m as the intermediate input layer in the full revenue account decomposition, illustrating that constant capital consumed in production is the largest component of TP*.</t>
+          <t>C*m = M'p = materials inputs into production... GVA* = TV* - C*m = Marxian gross value added.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Fig 5.4</t>
+          <t>ST_1994, Ch5, p.95; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>theoretical_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C*_m is the materials-flow (circulating) portion of constant capital. It excludes fixed capital depreciation, which enters through a separate channel. The distinction between C*_m and total constant capital C* (which includes depreciation of fixed capital) is critical for computing the value composition of capital.</t>
+          <t>C*m = M′p = materials inputs into production; C*d = {Dp} = depreciation of productive fixed capital; C* = M′p + Dp = constant capital used up (flow).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 pp.201-215; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_21/full_transcription.md; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_22/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No modern extension is available. Any future extension would require reconstructing productive-sector intermediate inputs from BEA Use tables, which demands a full sector concordance update.</t>
+          <t>Materials used up C*m and productive use U*m: Both net of depreciation. C*m = C* − Depreciation. Simply equal to M′p (sum of first two entries in top left corner of the IO table).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPR T502_DPR.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Figure 5.14 pursues the analysis of the central value categories by breaking down real total value into its principal components: TV* = C* + V* + S*, in 1982 constant dollars. By far the biggest component is C*, which is roughly 50% of total value.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Constant capital (materials) measures intermediate inputs of productive and trading sectors. Available only for 1948-1989 from Table E.2 with no modern extension.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>C*_m represents the intermediate inputs consumed by productive sectors (materials-flow constant capital). It is the sum of all intermediate purchases by productive and trading industries. C*_m = total intermediate inputs of productive + trading sectors from IO tables.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/tables/page_340_variables_definitions.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Subseries A only (1948-1989): digitized from book Table E.2. No extension subseries exists because detailed IO intermediate input data at the required sectoral granularity is not straightforwardly available from BEA for modern periods without full IO table reconstruction.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/tables/page_310_table_E2.csv</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig 5.4 shows C*_m as the intermediate input layer in the full revenue account decomposition, illustrating that constant capital consumed in production is the largest component of TP*.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Fig 5.4</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>theoretical_note</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>No extension beyond 1989 — requires full IO table reconstruction</t>
+          <t>C*_m is the materials-flow (circulating) portion of constant capital. It excludes fixed capital depreciation, which enters through a separate channel. The distinction between C*_m and total constant capital C* (which includes depreciation of fixed capital) is critical for computing the value composition of capital.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 pp.201-215; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_21/full_transcription.md; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_22/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fixed capital depreciation excluded (materials-flow only)</t>
+          <t>No modern extension is available. Any future extension would require reconstructing productive-sector intermediate inputs from BEA Use tables, which demands a full sector concordance update.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DPR T502_DPR.md</t>
         </is>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S501</t>
-        </is>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S503</t>
-        </is>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S510</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S513</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Constant capital (materials) measures intermediate inputs of productive and trading sectors. Available only for 1948-1989 from Table E.2 with no modern extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>No extension beyond 1989 — requires full IO table reconstruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fixed capital depreciation excluded (materials-flow only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S501</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S503</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S510</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S513</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1670,11 +2612,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1726,59 +2668,178 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>null — series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BEA</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>splice_year</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>growth_rate</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[0, 30000]</t>
+          <t>S502-EXT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S502-COMBINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations. Cambridge University Press. Ch. 5, Appendix H.1 (column Mp), pp. 324-327. Materials-only identity per p. 95: C*_m = M'_p is the value of intermediate non-labor produced inputs consumed by productive industries, distinct from depreciation D_p (which is the consumption of fixed capital, handled separately).", "shaikh_appendix_ref": "Appendix H.1, column Mp (1948-1989); pp. 324-327. Methodological discussion of M'_p construction in Ch. 5 main text and at the level of the IO/NIPA integration described in Appendix H.", "extension_source": "BEA GDP-by-Industry: Intermediate Inputs computed as Gross Output minus Value Added for productive+trade top-level NAICS industries (S502-EXT subseries). Industries: 11 (Agriculture), 21 (Mining), 22 (Utilities), 23 (Construction), 31G (Manufacturing rollup), 42 (Wholesale), 44RT (Retail), 48TW (Transportation+Warehousing). Cache files: gdp_by_industry_gross_output.csv, gdp_by_industry_value_added.csv at Inputs/ST2/Inputs/API_Data/BEA/, pulled 2026-02-24 by pull_bea_nipa_ch05.py.", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "C*_m / M'_p is the materials flow of productive constant capital \u2014 the value of intermediate non-labor produced inputs absorbed in production. BEA's identity II = GO - VA at the industry level is the modern accounting equivalent restricted to the productive partition. Both eras observe the same construct (value of intermediate inputs to productive industries) under different industrial classifications (SIC pre-1989 vs NAICS post-1997). Growth-rate splice is admissible per the Anu Extension Standard because II is a directly-observed flow, not a derived ratio. The only methodological adjustment is the SIC&lt;-&gt;NAICS productive-industry concordance (per S501 EPR Appendix C).", "vintage_note": "Book values 1948-1989 frozen at the book's vintage (SIC-based BEA NIPA + IO tables as published by 1993). Modern extension uses BEA GDP-by-Industry NAICS data 1997-2024, approximately the September 2025 NIPA vintage. The 1990-1996 gap is bridged log-linearly between the 1989 book endpoint (3278.25) and the 1997 BEA endpoint (3945.10), documented as M04_S502 in DIVERGENCE_REGISTER.json. The BEA endpoint exceeds the book endpoint by ~20%, consistent with normal trend growth plus comprehensive-revision level effects; the growth-rate splice preserves the post-1997 BEA growth profile."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>["gdp_by_industry_gross_output.csv", "gdp_by_industry_value_added.csv"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{"1948": 198.47, "1989": 3278.25, "1997": 3945.1, "2010": 5684.5, "2024": 9367.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[0, 30000]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>level_series</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S502.xlsx
+++ b/extenbooks/S502.xlsx
@@ -589,10 +589,10 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>261.3</v>
+        <v>261.36</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>261.3</v>
+        <v>261.36</v>
       </c>
       <c r="D9" s="3" t="n">
         <v/>
@@ -2612,10 +2612,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2843,6 +2843,18 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S502.xlsx
+++ b/extenbooks/S502.xlsx
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2855,6 +2855,18 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>reference_source</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1997/2010/2024 = II = GO - VA over partition A (BEA GDP-by-Industry); independently recomputed 2026-07-01 (exact). class=external (de-tautologized DIV-022).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S502.xlsx
+++ b/extenbooks/S502.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations. Cambridge University Press. Ch. 5, Appendix H.1 (column Mp), pp. 324-327. Materials-only identity per p. 95: C*_m = M'_p is the value of intermediate non-labor produced inputs consumed by productive industries, distinct from depreciation D_p (which is the consumption of fixed capital, handled separately).", "shaikh_appendix_ref": "Appendix H.1, column Mp (1948-1989); pp. 324-327. Methodological discussion of M'_p construction in Ch. 5 main text and at the level of the IO/NIPA integration described in Appendix H.", "extension_source": "BEA GDP-by-Industry: Intermediate Inputs computed as Gross Output minus Value Added for productive+trade top-level NAICS industries (S502-EXT subseries). Industries: 11 (Agriculture), 21 (Mining), 22 (Utilities), 23 (Construction), 31G (Manufacturing rollup), 42 (Wholesale), 44RT (Retail), 48TW (Transportation+Warehousing). Cache files: gdp_by_industry_gross_output.csv, gdp_by_industry_value_added.csv at Inputs/ST2/Inputs/API_Data/BEA/, pulled 2026-02-24 by pull_bea_nipa_ch05.py.", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "C*_m / M'_p is the materials flow of productive constant capital \u2014 the value of intermediate non-labor produced inputs absorbed in production. BEA's identity II = GO - VA at the industry level is the modern accounting equivalent restricted to the productive partition. Both eras observe the same construct (value of intermediate inputs to productive industries) under different industrial classifications (SIC pre-1989 vs NAICS post-1997). Growth-rate splice is admissible per the Anu Extension Standard because II is a directly-observed flow, not a derived ratio. The only methodological adjustment is the SIC&lt;-&gt;NAICS productive-industry concordance (per S501 EPR Appendix C).", "vintage_note": "Book values 1948-1989 frozen at the book's vintage (SIC-based BEA NIPA + IO tables as published by 1993). Modern extension uses BEA GDP-by-Industry NAICS data 1997-2024, approximately the September 2025 NIPA vintage. The 1990-1996 gap is bridged log-linearly between the 1989 book endpoint (3278.25) and the 1997 BEA endpoint (3945.10), documented as M04_S502 in DIVERGENCE_REGISTER.json. The BEA endpoint exceeds the book endpoint by ~20%, consistent with normal trend growth plus comprehensive-revision level effects; the growth-rate splice preserves the post-1997 BEA growth profile."}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations. Cambridge University Press. Ch. 5, Appendix H.1 (column Mp), pp. 324-327. Materials-only identity per p. 95: C*_m = M'_p is the value of intermediate non-labor produced inputs consumed by productive industries, distinct from depreciation D_p (which is the consumption of fixed capital, handled separately).", "shaikh_appendix_ref": "Appendix H.1, column Mp (1948-1989); pp. 324-327. Methodological discussion of M'_p construction in Ch. 5 main text and at the level of the IO/NIPA integration described in Appendix H.", "extension_source": "BEA GDP-by-Industry: Intermediate Inputs computed as Gross Output minus Value Added for productive+trade top-level NAICS industries (S502-EXT subseries). Industries: 11 (Agriculture), 21 (Mining), 22 (Utilities), 23 (Construction), 31G (Manufacturing rollup), 42 (Wholesale), 44RT (Retail), 48TW (Transportation+Warehousing). Cache files: gdp_by_industry_gross_output.csv, gdp_by_industry_value_added.csv at data/raw/Inputs/API_Data/BEA/, pulled 2026-02-24 by pull_bea_nipa_ch05.py.", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "C*_m / M'_p is the materials flow of productive constant capital \u2014 the value of intermediate non-labor produced inputs absorbed in production. BEA's identity II = GO - VA at the industry level is the modern accounting equivalent restricted to the productive partition. Both eras observe the same construct (value of intermediate inputs to productive industries) under different industrial classifications (SIC pre-1989 vs NAICS post-1997). Growth-rate splice is admissible per the Anu Extension Standard because II is a directly-observed flow, not a derived ratio. The only methodological adjustment is the SIC&lt;-&gt;NAICS productive-industry concordance (per S501 EPR Appendix C).", "vintage_note": "Book values 1948-1989 frozen at the book's vintage (SIC-based BEA NIPA + IO tables as published by 1993). Modern extension uses BEA GDP-by-Industry NAICS data 1997-2024, approximately the September 2025 NIPA vintage. The 1990-1996 gap is bridged log-linearly between the 1989 book endpoint (3278.25) and the 1997 BEA endpoint (3945.10), documented as M04_S502 in DIVERGENCE_REGISTER.json. The BEA endpoint exceeds the book endpoint by ~20%, consistent with normal trend growth plus comprehensive-revision level effects; the growth-rate splice preserves the post-1997 BEA growth profile."}</t>
         </is>
       </c>
     </row>
